--- a/source/internal/report/template.xlsx
+++ b/source/internal/report/template.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Pistol" sheetId="4" r:id="rId2"/>
     <sheet name="Revovler OS" sheetId="5" r:id="rId3"/>
     <sheet name="Pistol OS" sheetId="7" r:id="rId4"/>
-    <sheet name="Rifle" sheetId="6" r:id="rId5"/>
+    <sheet name="Carbine" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
